--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-terminologie-nuva.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-terminologie-nuva.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5727" uniqueCount="3833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5748" uniqueCount="3847">
   <si>
     <t>Property</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.946</t>
+    <t>1.0.992</t>
   </si>
   <si>
     <t>Name</t>
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-04T00:00:00+00:00</t>
+    <t>2025-09-08T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -131,7 +131,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>1875</t>
+    <t>1882</t>
   </si>
   <si>
     <t>Code</t>
@@ -1724,6 +1724,12 @@
     <t>TETAMUN SSW</t>
   </si>
   <si>
+    <t>VAL423</t>
+  </si>
+  <si>
+    <t>Valence covid 19, variant Omicron LP.8.1, ARNm codant la protéine de pointe du SARS-CoV-2</t>
+  </si>
+  <si>
     <t>VAC1103</t>
   </si>
   <si>
@@ -1802,6 +1808,12 @@
     <t>TICOVAC 0,25 mL</t>
   </si>
   <si>
+    <t>VAL424</t>
+  </si>
+  <si>
+    <t>Valence covid 19, variant Omicron LP.8.1, ARNm codant la protéine de pointe du SARS-CoV-2, 30 microgrammes</t>
+  </si>
+  <si>
     <t>VAC1322</t>
   </si>
   <si>
@@ -2282,6 +2294,12 @@
     <t>Valence pneumocoque, polyosidique non conjuguée, sérotype 2</t>
   </si>
   <si>
+    <t>VAL425</t>
+  </si>
+  <si>
+    <t>Valence covid 19, variant Omicron LP.8.1, ARNm codant la protéine de pointe du SARS-CoV-2, 10 microgrammes</t>
+  </si>
+  <si>
     <t>VAC0211</t>
   </si>
   <si>
@@ -2360,6 +2378,12 @@
     <t>VAXNEUVANCE</t>
   </si>
   <si>
+    <t>VAL426</t>
+  </si>
+  <si>
+    <t>Valence covid 19, variant Omicron LP.8.1, ARNm codant la protéine de pointe du SARS-CoV-2, 3 microgrammes</t>
+  </si>
+  <si>
     <t>VAC0030</t>
   </si>
   <si>
@@ -4514,6 +4538,12 @@
     <t>COMIRNATY KP.2 10 µg</t>
   </si>
   <si>
+    <t>VAC1466</t>
+  </si>
+  <si>
+    <t>COMIRNATY LP.8.1 30 µg</t>
+  </si>
+  <si>
     <t>VAC1200</t>
   </si>
   <si>
@@ -4592,6 +4622,12 @@
     <t>Vaccin Grippe, inactivé trivalent, haute dose, voie intradermique, sans précision</t>
   </si>
   <si>
+    <t>VAC1467</t>
+  </si>
+  <si>
+    <t>COMIRNATY LP.8.1 3 µg</t>
+  </si>
+  <si>
     <t>VAC1116</t>
   </si>
   <si>
@@ -4994,6 +5030,12 @@
     <t>Vaccin Covid 19 bivalent à ARNm contre le virus originel et le variant Omicron BA.4/5, 5 microgrammes, sans précision</t>
   </si>
   <si>
+    <t>VAC1468</t>
+  </si>
+  <si>
+    <t>COMIRNATY LP.8.1 10 µg</t>
+  </si>
+  <si>
     <t>VAC0573</t>
   </si>
   <si>
@@ -8789,7 +8831,7 @@
     <t>VAC0649</t>
   </si>
   <si>
-    <t>EFLUELDA QIV-HD</t>
+    <t>EFLUELDA TETRA</t>
   </si>
   <si>
     <t>VAC0516</t>
@@ -12077,7 +12119,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1876"/>
+  <dimension ref="A1:D1883"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -34594,6 +34636,90 @@
       </c>
       <c r="D1876" s="2"/>
     </row>
+    <row r="1877">
+      <c r="A1877" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B1877" t="s" s="2">
+        <v>3833</v>
+      </c>
+      <c r="C1877" t="s" s="2">
+        <v>3834</v>
+      </c>
+      <c r="D1877" s="2"/>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B1878" t="s" s="2">
+        <v>3835</v>
+      </c>
+      <c r="C1878" t="s" s="2">
+        <v>3836</v>
+      </c>
+      <c r="D1878" s="2"/>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B1879" t="s" s="2">
+        <v>3837</v>
+      </c>
+      <c r="C1879" t="s" s="2">
+        <v>3838</v>
+      </c>
+      <c r="D1879" s="2"/>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B1880" t="s" s="2">
+        <v>3839</v>
+      </c>
+      <c r="C1880" t="s" s="2">
+        <v>3840</v>
+      </c>
+      <c r="D1880" s="2"/>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B1881" t="s" s="2">
+        <v>3841</v>
+      </c>
+      <c r="C1881" t="s" s="2">
+        <v>3842</v>
+      </c>
+      <c r="D1881" s="2"/>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B1882" t="s" s="2">
+        <v>3843</v>
+      </c>
+      <c r="C1882" t="s" s="2">
+        <v>3844</v>
+      </c>
+      <c r="D1882" s="2"/>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B1883" t="s" s="2">
+        <v>3845</v>
+      </c>
+      <c r="C1883" t="s" s="2">
+        <v>3846</v>
+      </c>
+      <c r="D1883" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
